--- a/supporting_material/experiments/favalli/favalli.xlsx
+++ b/supporting_material/experiments/favalli/favalli.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/favelli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/favalli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AEED09-6967-BD4E-B691-95E34A9D1872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428CC449-EE21-E14F-BA0D-030C21553989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1891,9 +1891,6 @@
     <t>AG24_243</t>
   </si>
   <si>
-    <t>/users/amarti51/projects/delt-hit/supporting_material/experiments</t>
-  </si>
-  <si>
     <t>CGAGTCCCATGGCGCCGGATCGACG</t>
   </si>
   <si>
@@ -3547,10 +3544,13 @@
     <t>TGGCAAT</t>
   </si>
   <si>
-    <t>/users/amarti51/projects/delt-hit/supporting_material/favalli/favalli.fastq.gz</t>
-  </si>
-  <si>
     <t>favalli</t>
+  </si>
+  <si>
+    <t>/users/amarti51/projects/delt-hit/supporting_material/experiments/favalli/favalli.fastq.gz</t>
+  </si>
+  <si>
+    <t>/users/amarti51/projects/delt-hit/supporting_material/experiments/</t>
   </si>
 </sst>
 </file>
@@ -4248,7 +4248,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -4264,7 +4264,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>615</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -7558,7 +7558,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -7566,7 +7566,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -9481,7 +9481,7 @@
     </row>
     <row r="300" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="46" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F300" s="2"/>
     </row>
@@ -10725,2742 +10725,2742 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="38" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="38" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="38" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="38" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="38" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="38" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="38" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="38" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="38" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="38" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="38" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="38" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="38" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="38" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="38" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="38" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="38" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="38" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="38" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="38" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="38" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="38" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="38" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="38" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="38" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="38" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="38" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="38" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="38" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="38" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="38" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="38" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="38" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="38" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="38" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="38" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="38" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="38" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="38" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="38" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="38" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="38" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="38" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="38" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="38" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="38" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="38" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="38" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="38" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="38" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="38" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="38" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="38" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="38" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="38" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="38" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="38" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="38" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="38" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="38" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="38" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="38" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="38" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="38" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="38" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="38" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="38" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="38" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="38" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="38" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="38" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="38" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="38" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="38" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="38" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="38" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="38" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="38" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="38" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="38" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="38" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="38" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="38" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="38" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="38" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="38" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="38" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="38" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="38" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="38" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="38" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="38" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="38" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="38" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="38" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="38" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="38" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="38" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="38" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="38" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="38" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="38" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="38" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="38" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="38" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="38" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="38" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="38" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="38" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="38" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="38" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="38" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="38" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="38" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="38" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="38" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="38" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="38" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="38" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="38" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="38" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="38" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="38" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="38" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="38" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="38" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="38" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="38" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="38" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="38" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="38" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="38" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="38" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="38" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="38" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="38" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="38" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="38" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="38" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="38" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="38" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="38" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="38" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="38" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="38" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="38" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="38" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="38" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="38" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="38" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="38" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="38" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="38" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="38" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="38" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="38" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="38" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="38" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="38" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="38" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="38" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="38" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="38" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="38" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="38" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="38" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="38" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="38" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="38" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" s="38" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" s="38" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" s="38" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" s="38" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" s="38" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" s="38" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" s="38" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" s="38" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" s="38" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" s="38" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" s="38" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" s="38" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" s="38" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" s="38" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" s="38" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" s="38" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" s="38" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" s="38" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" s="38" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" s="38" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" s="38" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" s="38" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" s="38" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" s="38" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" s="38" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" s="38" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" s="38" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" s="38" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" s="38" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" s="38" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" s="38" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" s="38" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" s="38" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" s="38" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" s="38" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" s="38" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" s="38" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" s="38" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" s="38" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" s="38" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" s="38" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" s="38" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" s="38" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" s="38" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" s="38" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" s="38" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A245" s="38" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A246" s="38" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A247" s="38" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A248" s="38" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A249" s="38" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A250" s="38" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A251" s="38" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A252" s="38" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A253" s="38" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A254" s="38" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A255" s="38" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A256" s="38" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" s="38" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" s="38" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" s="38" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" s="38" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" s="38" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" s="38" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" s="38" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" s="38" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" s="38" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" s="38" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" s="38" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" s="38" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" s="38" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" s="38" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" s="38" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" s="38" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" s="38" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" s="38" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" s="38" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" s="38" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" s="38" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" s="38" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" s="38" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" s="38" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" s="38" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" s="38" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" s="38" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" s="38" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" s="38" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" s="38" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" s="38" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" s="38" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" s="38" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" s="38" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" s="38" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" s="38" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" s="38" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" s="38" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" s="38" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" s="38" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" s="38" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" s="38" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" s="38" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" s="38" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" s="38" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" s="38" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" s="38" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" s="38" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" s="38" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" s="38" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" s="38" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" s="38" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" s="38" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" s="38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" s="38" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" s="38" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" s="38" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" s="38" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" s="38" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" s="38" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" s="38" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" s="38" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" s="38" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" s="38" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" s="38" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" s="38" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" s="38" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" s="38" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" s="38" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" s="38" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" s="38" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" s="38" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" s="38" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" s="38" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" s="38" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" s="38" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" s="38" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" s="38" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" s="38" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" s="38" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" s="38" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" s="38" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" s="38" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" s="38" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" s="38" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" s="38" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" s="38" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" s="38" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" s="38" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" s="38" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" s="38" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" s="38" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" s="38" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" s="38" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" s="38" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" s="38" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" s="38" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" s="38" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" s="38" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" s="38" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" s="38" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" s="38" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" s="38" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" s="38" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" s="38" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" s="38" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" s="38" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" s="38" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" s="38" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" s="38" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" s="38" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" s="38" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" s="38" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" s="38" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" s="38" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" s="38" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" s="38" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" s="38" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" s="38" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" s="38" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" s="38" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" s="38" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" s="38" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" s="38" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" s="38" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" s="38" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" s="38" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" s="38" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A386" s="38" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A387" s="38" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A388" s="38" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A389" s="38" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A390" s="38" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A391" s="38" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A392" s="38" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A393" s="38" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A394" s="38" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A395" s="38" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A396" s="38" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A397" s="38" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A398" s="38" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A399" s="38" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A400" s="38" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A401" s="38" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A402" s="38" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A403" s="38" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A404" s="38" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A405" s="38" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A406" s="38" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A407" s="38" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A408" s="38" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A409" s="38" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A410" s="38" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A411" s="38" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A412" s="38" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A413" s="38" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A414" s="38" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A415" s="38" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A416" s="38" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" s="38" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" s="38" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" s="38" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" s="38" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" s="38" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" s="38" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" s="38" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" s="38" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" s="38" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" s="38" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" s="38" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" s="38" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" s="38" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" s="38" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A431" s="38" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A432" s="38" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A433" s="38" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A434" s="38" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A435" s="38" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A436" s="38" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A437" s="38" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A438" s="38" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A439" s="38" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A440" s="38" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A441" s="38" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A442" s="38" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A443" s="38" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A444" s="38" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A445" s="38" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A446" s="38" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A447" s="38" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A448" s="38" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A449" s="38" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A450" s="38" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A451" s="38" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A452" s="38" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A453" s="38" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A454" s="38" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A455" s="38" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A456" s="38" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A457" s="38" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A458" s="38" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A459" s="38" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A460" s="38" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A461" s="38" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A462" s="38" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A463" s="38" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A464" s="38" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A465" s="38" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A466" s="38" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A467" s="38" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A468" s="38" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A469" s="38" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A470" s="38" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A471" s="38" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A472" s="38" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A473" s="38" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A474" s="38" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A475" s="38" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A476" s="38" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A477" s="38" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A478" s="38" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A479" s="38" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A480" s="38" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A481" s="38" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A482" s="38" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A483" s="38" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A484" s="38" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A485" s="38" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A486" s="38" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A487" s="38" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A488" s="38" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A489" s="38" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A490" s="38" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A491" s="38" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A492" s="38" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A493" s="38" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A494" s="38" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A495" s="38" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A496" s="38" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A497" s="38" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A498" s="38" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A499" s="38" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A500" s="38" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A501" s="38" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A502" s="38" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A503" s="38" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A504" s="38" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A505" s="38" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A506" s="38" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A507" s="38" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A508" s="38" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A509" s="38" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A510" s="38" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A511" s="38" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A512" s="38" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A513" s="38" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A514" s="38" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A515" s="38" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A516" s="38" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A517" s="38" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A518" s="38" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A519" s="38" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A520" s="38" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A521" s="38" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A522" s="38" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A523" s="38" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A524" s="38" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A525" s="38" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A526" s="38" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A527" s="38" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A528" s="38" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A529" s="38" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A530" s="38" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A531" s="38" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A532" s="38" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A533" s="38" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A534" s="38" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A535" s="38" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A536" s="38" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A537" s="38" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A538" s="38" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A539" s="38" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A540" s="38" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A541" s="38" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A542" s="38" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A543" s="38" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A544" s="38" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A545" s="38" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A546" s="38" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A547" s="38" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A548" s="38" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A549" s="38" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.2">
